--- a/diseases/d021/2000-2004.xlsx
+++ b/diseases/d021/2000-2004.xlsx
@@ -49858,11 +49858,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
-        </is>
-      </c>
       <c r="AA299" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49875,7 +49870,7 @@
       </c>
       <c r="AP299" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ299" t="inlineStr">
@@ -49885,15 +49880,15 @@
       </c>
       <c r="AS299" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
+          <t>SER_CN_PROV_DC_DENGUE; SER_CN_PROV_REPORT_DENGUE</t>
         </is>
       </c>
       <c r="AT299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV299" t="inlineStr">
@@ -50109,7 +50104,7 @@
       </c>
       <c r="AP300" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ300" t="inlineStr">
@@ -50119,15 +50114,15 @@
       </c>
       <c r="AS300" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
+          <t>SER_CN_PROV_DC_DENGUE; SER_CN_PROV_REPORT_DENGUE</t>
         </is>
       </c>
       <c r="AT300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV300" t="inlineStr">
@@ -54053,11 +54048,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
-        </is>
-      </c>
       <c r="AA324" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -54070,7 +54060,7 @@
       </c>
       <c r="AP324" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ324" t="inlineStr">
@@ -54080,15 +54070,15 @@
       </c>
       <c r="AS324" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
+          <t>SER_CN_PROV_DC_DENGUE; SER_CN_PROV_REPORT_DENGUE</t>
         </is>
       </c>
       <c r="AT324" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV324" t="inlineStr">
@@ -54304,7 +54294,7 @@
       </c>
       <c r="AP325" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ325" t="inlineStr">
@@ -54314,15 +54304,15 @@
       </c>
       <c r="AS325" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
+          <t>SER_CN_PROV_DC_DENGUE; SER_CN_PROV_REPORT_DENGUE</t>
         </is>
       </c>
       <c r="AT325" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU325" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV325" t="inlineStr">
@@ -60578,11 +60568,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
-        </is>
-      </c>
       <c r="AA361" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -60595,7 +60580,7 @@
       </c>
       <c r="AP361" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ361" t="inlineStr">
@@ -60605,15 +60590,15 @@
       </c>
       <c r="AS361" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
+          <t>SER_CN_PROV_DC_DENGUE; SER_CN_PROV_REPORT_DENGUE</t>
         </is>
       </c>
       <c r="AT361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU361" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV361" t="inlineStr">
@@ -60829,7 +60814,7 @@
       </c>
       <c r="AP362" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ362" t="inlineStr">
@@ -60839,15 +60824,15 @@
       </c>
       <c r="AS362" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
+          <t>SER_CN_PROV_DC_DENGUE; SER_CN_PROV_REPORT_DENGUE</t>
         </is>
       </c>
       <c r="AT362" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU362" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV362" t="inlineStr">
@@ -63658,11 +63643,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
-        </is>
-      </c>
       <c r="AA378" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -63675,7 +63655,7 @@
       </c>
       <c r="AP378" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ378" t="inlineStr">
@@ -63685,15 +63665,15 @@
       </c>
       <c r="AS378" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
+          <t>SER_CN_PROV_DC_DENGUE; SER_CN_PROV_REPORT_DENGUE</t>
         </is>
       </c>
       <c r="AT378" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU378" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV378" t="inlineStr">
@@ -63909,7 +63889,7 @@
       </c>
       <c r="AP379" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ379" t="inlineStr">
@@ -63919,15 +63899,15 @@
       </c>
       <c r="AS379" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
+          <t>SER_CN_PROV_DC_DENGUE; SER_CN_PROV_REPORT_DENGUE</t>
         </is>
       </c>
       <c r="AT379" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU379" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV379" t="inlineStr">
@@ -66733,11 +66713,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
-        </is>
-      </c>
       <c r="AA395" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -66750,7 +66725,7 @@
       </c>
       <c r="AP395" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ395" t="inlineStr">
@@ -66760,15 +66735,15 @@
       </c>
       <c r="AS395" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
+          <t>SER_CN_PROV_DC_DENGUE; SER_CN_PROV_REPORT_DENGUE</t>
         </is>
       </c>
       <c r="AT395" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU395" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV395" t="inlineStr">
@@ -66984,7 +66959,7 @@
       </c>
       <c r="AP396" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ396" t="inlineStr">
@@ -66994,15 +66969,15 @@
       </c>
       <c r="AS396" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
+          <t>SER_CN_PROV_DC_DENGUE; SER_CN_PROV_REPORT_DENGUE</t>
         </is>
       </c>
       <c r="AT396" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU396" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV396" t="inlineStr">
@@ -70188,11 +70163,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
-        </is>
-      </c>
       <c r="AA414" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -70205,7 +70175,7 @@
       </c>
       <c r="AP414" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ414" t="inlineStr">
@@ -70215,15 +70185,15 @@
       </c>
       <c r="AS414" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
+          <t>SER_CN_PROV_DC_DENGUE; SER_CN_PROV_REPORT_DENGUE</t>
         </is>
       </c>
       <c r="AT414" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU414" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV414" t="inlineStr">
@@ -70439,7 +70409,7 @@
       </c>
       <c r="AP415" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ415" t="inlineStr">
@@ -70449,15 +70419,15 @@
       </c>
       <c r="AS415" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
+          <t>SER_CN_PROV_DC_DENGUE; SER_CN_PROV_REPORT_DENGUE</t>
         </is>
       </c>
       <c r="AT415" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU415" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV415" t="inlineStr">
@@ -72488,11 +72458,6 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
-        </is>
-      </c>
       <c r="AA427" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -72505,7 +72470,7 @@
       </c>
       <c r="AP427" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ427" t="inlineStr">
@@ -72515,15 +72480,15 @@
       </c>
       <c r="AS427" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
+          <t>SER_CN_PROV_DC_DENGUE; SER_CN_PROV_REPORT_DENGUE</t>
         </is>
       </c>
       <c r="AT427" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU427" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV427" t="inlineStr">
@@ -72739,7 +72704,7 @@
       </c>
       <c r="AP428" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ428" t="inlineStr">
@@ -72749,15 +72714,15 @@
       </c>
       <c r="AS428" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_DENGUE</t>
+          <t>SER_CN_PROV_DC_DENGUE; SER_CN_PROV_REPORT_DENGUE</t>
         </is>
       </c>
       <c r="AT428" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU428" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV428" t="inlineStr">
